--- a/students_data.xlsx
+++ b/students_data.xlsx
@@ -413,18 +413,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>اسم الطالب</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>السجل المدني</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>اسم الطالب</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -441,17 +441,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1169565965</t>
+          <t>أحمد بن علي بن أحمد خواجي</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>أحمد بن يحي بن جبريل دريب</t>
+          <t>1170306805</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>السادس الابتدائي</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -461,17 +461,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1167796265</t>
+          <t>المنذر بن ابراهيم بن أحمد بن نعمان</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>أسامه موسي محمد شبير</t>
+          <t>1173444488</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>السادس الابتدائي</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -481,17 +481,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1169588595</t>
+          <t>اياد هادي يحي علي</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>أنس محمد علي دربشي</t>
+          <t>2392682916</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>السادس الابتدائي</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -501,17 +501,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1171563800</t>
+          <t>اياس بن ابراهيم بن حسين الامير</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>أيهم بن عبده بن عبدالله موز</t>
+          <t>1175848421</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>السادس الابتدائي</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -521,17 +521,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1166856441</t>
+          <t>ايمن بن وحيد بن علي بن فقيه</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>امير بن يحيى بن محمد عزيبي</t>
+          <t>2401730763</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>السادس الابتدائي</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -541,17 +541,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1169201884</t>
+          <t>جواد بن حسن حسين بن شولان</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>حسن بن محمد بن حسين خواجي</t>
+          <t>1171842535</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>السادس الابتدائي</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -561,17 +561,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1174949253</t>
+          <t>جواد خليل محمد البعداني</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>حسين محمد حسين خواجي</t>
+          <t>6054986601</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>السادس الابتدائي</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -581,17 +581,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1170974438</t>
+          <t>حازم بن عبده بن عايض بن صيادي</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>حمد بن عبدالله بن حمد طميحي</t>
+          <t>1173283431</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>السادس الابتدائي</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -601,17 +601,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1169035720</t>
+          <t>حافظ بن عبدالله بن علي بن شولان</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>خالد بن هاني بن محمد مخضري</t>
+          <t>1167084365</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>السادس الابتدائي</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -621,17 +621,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1170643603</t>
+          <t>حسن بن محسن بن حسن جمعان</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>خليل بن إبراهيم بن مضوي فقيهي</t>
+          <t>1214683276</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>السادس الابتدائي</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -641,17 +641,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1169175351</t>
+          <t>خالد حسين محمد محزوم</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>راكان بن يحي بن حسن معدلي</t>
+          <t>1159694486</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>السادس الابتدائي</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -661,17 +661,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1171833401</t>
+          <t>رمزي محمد علي فقيه</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>سلطان حسين علي خواجي</t>
+          <t>2401728494</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>السادس الابتدائي</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -681,17 +681,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1170687485</t>
+          <t>ريان حسن موسى انصاري</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>صبري بن ماجد بن رزق الله راجحي</t>
+          <t>1169574892</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>السادس الابتدائي</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -701,17 +701,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1170228157</t>
+          <t>ضيف الله بن ادريس بن احمد بن حسن جبريل بصيلي</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>طراد بن علي بن عطية نجمي</t>
+          <t>1172460063</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>السادس الابتدائي</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -721,17 +721,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1192127726</t>
+          <t>طلال محمد جردي خبراني</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>عادل بن حبيب بن حسن خواجي</t>
+          <t>1163976796</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>السادس الابتدائي</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -741,17 +741,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1169689138</t>
+          <t>عبدالحافظ رديف ناصر ريثي</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>عبدالرحمن ابن محمد بن عيسى بن عبده عيساوي</t>
+          <t>1173719897</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>السادس الابتدائي</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -761,17 +761,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1171596792</t>
+          <t>عبدالرحمن احمد علي فقيه</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>عبدالرحمن بن أحمد بن علي خواجي</t>
+          <t>1169588116</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>السادس الابتدائي</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -781,17 +781,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1168669255</t>
+          <t>عبدالرحمن محمد بن علي السلمى</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>عبدالعزيز فهد علي عامري</t>
+          <t>1172872523</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>السادس الابتدائي</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -801,17 +801,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1172262048</t>
+          <t>عبدالله عطيه بن محمد نجمي</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>عبدالوهاب بن علي بن محمد طوهري</t>
+          <t>1174862340</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>السادس الابتدائي</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -821,17 +821,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1185031505</t>
+          <t>قصي يحى جبريل دريب</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>علي بن ابراهيم بن حسن شبيلي</t>
+          <t>1174137776</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>السادس الابتدائي</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -841,17 +841,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1168688891</t>
+          <t>مؤيد عبدالله ابوشلعه دايلي</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>علي بن محمد بن حسين خواجي</t>
+          <t>1177349022</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>السادس الابتدائي</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -861,17 +861,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1166210987</t>
+          <t>محمد حسن محمد فقيه</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>علي صهيف علي نعمان</t>
+          <t>1173197995</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>السادس الابتدائي</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -881,17 +881,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1168095436</t>
+          <t>محمد يونس علي فقيه</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>عمر بن يحي بن محمد قاتله</t>
+          <t>2419308123</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>السادس الابتدائي</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -901,17 +901,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1171713983</t>
+          <t>مهند حسن علي شتيفي</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>عيسى بن رديف بن عيسى بن ناصر جمعان</t>
+          <t>1172665190</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>السادس الابتدائي</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -921,17 +921,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1168991279</t>
+          <t>موسى جابر علي ذماري</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>فهد بن فواز بن حسين شولان</t>
+          <t>1171720475</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>السادس الابتدائي</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -941,17 +941,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1169263223</t>
+          <t>أحمد بن يحي بن جبريل دريب</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>فواز بن نوح بن إبراهيم خواجي</t>
+          <t>1169565965</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الأول المتوسط</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -961,17 +961,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1169852983</t>
+          <t>أسامه موسي محمد شبير</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>فيصل بن أبو طالب بن حسين النعمان</t>
+          <t>1167796265</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الأول المتوسط</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -981,17 +981,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1169454954</t>
+          <t>أنس محمد علي دربشي</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>مالك بن مروان بن مكي محمد</t>
+          <t>1169588595</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الأول المتوسط</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1001,17 +1001,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1166954410</t>
+          <t>أيهم بن عبده بن عبدالله موز</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>أحمد بن نايف بن احمد بن حاج بن دبه عاتي</t>
+          <t>1171563800</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الأول المتوسط</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1021,17 +1021,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1167910759</t>
+          <t>امير بن يحيى بن محمد عزيبي</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ابراهيم خليل ابراهيم خواجي</t>
+          <t>1166856441</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الأول المتوسط</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1041,17 +1041,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1164119099</t>
+          <t>حسن بن محمد بن حسين خواجي</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>احمد بن جابر بن محمد مرزوق</t>
+          <t>1169201884</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الأول المتوسط</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1061,17 +1061,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1165851203</t>
+          <t>حسين محمد حسين خواجي</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>احمد بن حواس بن حسن فقيه</t>
+          <t>1174949253</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الأول المتوسط</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1081,17 +1081,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1187248495</t>
+          <t>حمد بن عبدالله بن حمد طميحي</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>احمد بن عادل بن حمد عاتي</t>
+          <t>1170974438</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الأول المتوسط</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1101,17 +1101,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1165767623</t>
+          <t>خالد بن هاني بن محمد مخضري</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>احمد بن علي بن مروعي خواجي</t>
+          <t>1169035720</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الأول المتوسط</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1121,17 +1121,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1163250507</t>
+          <t>خليل بن إبراهيم بن مضوي فقيهي</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>احمد بن قاسم بن محمد الاعرج</t>
+          <t>1170643603</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الأول المتوسط</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1141,17 +1141,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2358182216</t>
+          <t>راكان بن يحي بن حسن معدلي</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>البراء علي ابراهيم مسروحي</t>
+          <t>1169175351</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الأول المتوسط</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1161,17 +1161,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1164745075</t>
+          <t>سلطان حسين علي خواجي</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>المعتصم بن محمد بن احمد خواجي</t>
+          <t>1171833401</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الأول المتوسط</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1181,17 +1181,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1162636409</t>
+          <t>صبري بن ماجد بن رزق الله راجحي</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>الهثيم بن عبد الله بن يحي النجادي</t>
+          <t>1170687485</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الأول المتوسط</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1201,17 +1201,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1166713774</t>
+          <t>طراد بن علي بن عطية نجمي</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>اليزن بن احمد بن محمد بن حسن شويعي</t>
+          <t>1170228157</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الأول المتوسط</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1221,17 +1221,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1166320125</t>
+          <t>عادل بن حبيب بن حسن خواجي</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>جابر بن علي بن موسئ محش</t>
+          <t>1192127726</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الأول المتوسط</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1241,17 +1241,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1161921554</t>
+          <t>عبدالرحمن ابن محمد بن عيسى بن عبده عيساوي</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>جهاد بن حسين بن يحي ابوشرحه</t>
+          <t>1169689138</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الأول المتوسط</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1261,17 +1261,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1163615329</t>
+          <t>عبدالرحمن بن أحمد بن علي خواجي</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>جواد بن خليل بن ابراهيم عاتي</t>
+          <t>1171596792</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الأول المتوسط</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1281,17 +1281,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1165767011</t>
+          <t>عبدالعزيز فهد علي عامري</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>جواد هادي احمد عاتي</t>
+          <t>1168669255</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الأول المتوسط</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1301,17 +1301,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1162520587</t>
+          <t>عبدالوهاب بن علي بن محمد طوهري</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>حسن عبدالله حسين شولان</t>
+          <t>1172262048</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الأول المتوسط</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1321,17 +1321,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1163640749</t>
+          <t>علي ابراهيم عبده جلحوف</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>حسين بن حسن بن حسين بن حسن شولان</t>
+          <t>4157005325</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الأول المتوسط</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -1341,17 +1341,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1161636780</t>
+          <t>علي بن ابراهيم بن حسن شبيلي</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>سند بن حسن بن يحي مهنا</t>
+          <t>1185031505</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الأول المتوسط</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -1361,17 +1361,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1165358597</t>
+          <t>علي بن محمد بن حسين خواجي</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>عبد الرحيم بن محمد بن عبده سعد</t>
+          <t>1168688891</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الأول المتوسط</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -1381,17 +1381,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1166294825</t>
+          <t>علي صهيف علي نعمان</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>عبد العزيز بن علي بن عايل قميري</t>
+          <t>1166210987</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الأول المتوسط</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -1401,17 +1401,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1166320117</t>
+          <t>عمر بن يحي بن محمد قاتله</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>عبد العزيز بن علي بن موسئ محش</t>
+          <t>1168095436</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الأول المتوسط</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -1421,17 +1421,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1160946354</t>
+          <t>عيسى بن رديف بن عيسى بن ناصر جمعان</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>عبد العزيز بن مراد بن شمسي العمري</t>
+          <t>1171713983</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الأول المتوسط</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -1441,17 +1441,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1164815753</t>
+          <t>فهد بن فواز بن حسين شولان</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>علي بن بشير بن احمد بن محمد خواجي</t>
+          <t>1168991279</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الأول المتوسط</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -1461,17 +1461,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1158783835</t>
+          <t>فواز بن نوح بن إبراهيم خواجي</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>أيهم احمد عباس مسلم</t>
+          <t>1169263223</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الأول المتوسط</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -1481,17 +1481,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1156356238</t>
+          <t>فيصل بن أبو طالب بن حسين النعمان</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ابراهيم عبدالله حسن شبيلي</t>
+          <t>1169852983</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الأول المتوسط</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1501,17 +1501,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1158394609</t>
+          <t>مالك بن مروان بن مكي محمد</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ابراهيم محمد مشبي آل هيازع</t>
+          <t>1169454954</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الأول المتوسط</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -1521,421 +1521,1041 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1162251225</t>
+          <t>أحمد بن نايف بن احمد بن حاج بن دبه عاتي</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>المعتصم سعود منصور هوداني</t>
+          <t>1166954410</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الثاني المتوسط</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1156784439</t>
+          <t>أحمد عبدالله احمد فقيه</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>امجد محمد زيلعي فرنتي</t>
+          <t>0160201974</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الثاني المتوسط</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1161482110</t>
+          <t>أيمن عيسى علي مخضري</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>تركي علي مروعي خواجي</t>
+          <t>9025114404</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الثاني المتوسط</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1160152821</t>
+          <t>ابراهيم خليل ابراهيم خواجي</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>تيسير رابي محمد بحران</t>
+          <t>1167910759</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الثاني المتوسط</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1158394666</t>
+          <t>احمد بن جابر بن محمد مرزوق</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>خالد محمد مشبي آل هيازع</t>
+          <t>1164119099</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الثاني المتوسط</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1161432032</t>
+          <t>احمد بن حواس بن حسن فقيه</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ريان محمد حسين خواجي</t>
+          <t>1165851203</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الثاني المتوسط</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1160244859</t>
+          <t>احمد بن عادل بن حمد عاتي</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>سامي يحي هادي خمج</t>
+          <t>1187248495</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الثاني المتوسط</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1160370001</t>
+          <t>احمد بن علي بن مروعي خواجي</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>عبدالعزيز علي ابوطالب النعمان</t>
+          <t>1165767623</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الثاني المتوسط</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1173764992</t>
+          <t>البراء علي ابراهيم مسروحي</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>عبدالعزيز علي ابوطالب عر</t>
+          <t>2358182216</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الثاني المتوسط</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1161012891</t>
+          <t>المعتصم بن محمد بن احمد خواجي</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>عبدالله جراد ابراهيم عاتي</t>
+          <t>1164745075</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الثاني المتوسط</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1161524341</t>
+          <t>الهثيم بن عبد الله بن يحي النجادي</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>عبدالملك هادي بن محمد عاتي</t>
+          <t>1162636409</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الثاني المتوسط</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1148647421</t>
+          <t>اليزن بن احمد بن محمد بن حسن شويعي</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>عثمان محمد عثمان عاتي</t>
+          <t>1166713774</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الثاني المتوسط</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1160021273</t>
+          <t>ايمن محمد محمد دهل</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>علي حسن محمد خواجي</t>
+          <t>4144344068</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الثاني المتوسط</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1157152446</t>
+          <t>جابر بن علي بن موسئ محش</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>علي يحى محمد قاتله</t>
+          <t>1166320125</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الثاني المتوسط</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1162884520</t>
+          <t>جهاد بن حسين بن يحي ابوشرحه</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>عماد الزاهد عبدالله حمدي</t>
+          <t>1161921554</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الثاني المتوسط</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1163922105</t>
+          <t>جواد بن خليل بن ابراهيم عاتي</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>عمار سلطان دربي حريصي</t>
+          <t>1163615329</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الثاني المتوسط</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1162721680</t>
+          <t>جواد هادي احمد عاتي</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>عمر عبدالكريم عبدالله الهروبي</t>
+          <t>1165767011</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الثاني المتوسط</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1168939112</t>
+          <t>حسن عبدالله حسين شولان</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>فهد ماجد حسن خواجي</t>
+          <t>1162520587</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الثاني المتوسط</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1160973044</t>
+          <t>حسين بن حسن بن حسين بن حسن شولان</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>محمد ناصر متعب مشاري</t>
+          <t>1163640749</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الثاني المتوسط</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1159841939</t>
+          <t>ريان منصور هندي كردي</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>محمد نوح ابراهيم خواجي</t>
+          <t>4157601271</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>متوسطة الشقيري</t>
+          <t>الثاني المتوسط</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>سند بن حسن بن يحي مهنا</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1161636780</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>الثاني المتوسط</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>عبد الرحيم بن محمد بن عبده سعد</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1165358597</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>الثاني المتوسط</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>عبد العزيز بن علي بن عايل قميري</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1166294825</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>الثاني المتوسط</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>عبد العزيز بن علي بن موسئ محش</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1166320117</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>الثاني المتوسط</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>عبد العزيز بن مراد بن شمسي العمري</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1160946354</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>الثاني المتوسط</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>علي بن بشير بن احمد بن محمد خواجي</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1164815753</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>الثاني المتوسط</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>أيهم احمد عباس مسلم</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1158783835</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>الثالث المتوسط</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ابراهيم عبدالله حسن شبيلي</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1156356238</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>الثالث المتوسط</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>ابراهيم محمد مشبي آل هيازع</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1158394609</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>الثالث المتوسط</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>المعتصم سعود منصور هوداني</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1162251225</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>الثالث المتوسط</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>امجد محمد زيلعي فرنتي</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1156784439</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>الثالث المتوسط</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>تركي علي مروعي خواجي</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1161482110</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>الثالث المتوسط</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>تيسير رابي محمد بحران</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1160152821</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>الثالث المتوسط</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>خالد محمد مشبي آل هيازع</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1158394666</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>الثالث المتوسط</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ريان محمد حسين خواجي</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1161432032</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>الثالث المتوسط</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>سامي يحي هادي خمج</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1160244859</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>الثالث المتوسط</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>عبدالعزيز علي ابوطالب النعمان</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1160370001</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>الثالث المتوسط</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>عبدالعزيز علي ابوطالب عر</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1173764992</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>الثالث المتوسط</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>عبدالله جراد ابراهيم عاتي</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1161012891</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>الثالث المتوسط</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>عبدالله عبدالرحمن حمد رصاعي</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>0160736852</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>الثالث المتوسط</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>عبدالملك هادي بن محمد عاتي</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1161524341</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>الثالث المتوسط</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>عثمان محمد عثمان عاتي</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1148647421</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>الثالث المتوسط</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>علي حسن محمد خواجي</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1160021273</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>الثالث المتوسط</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>علي يحى محمد قاتله</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1157152446</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>الثالث المتوسط</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>عماد الزاهد عبدالله حمدي</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1162884520</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>الثالث المتوسط</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>عمار سلطان دربي حريصي</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1163922105</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>الثالث المتوسط</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>عمر عبدالكريم عبدالله الهروبي</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1162721680</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>الثالث المتوسط</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>غالب ماجد علي ال حسين</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>3912686530</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>الثالث المتوسط</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>فهد ماجد حسن خواجي</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1168939112</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>الثالث المتوسط</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>محمد ناصر متعب مشاري</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1160973044</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>الثالث المتوسط</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>محمد نوح ابراهيم خواجي</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1159841939</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>الثالث المتوسط</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>مشعل محمد علي بحران</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
           <t>1159319043</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>مشعل محمد علي بحران</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>متوسطة الشقيري</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>75</v>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>الثالث المتوسط</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/students_data.xlsx
+++ b/students_data.xlsx
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="58">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="59">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="61">
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62">
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="63">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="64">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="65">
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="66">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="67">
@@ -1755,7 +1755,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
     <row r="68">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="69">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="70">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
     </row>
     <row r="71">
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="72">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="73">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="74">
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="75">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="76">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="77">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="78">
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="79">
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="80">
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="81">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="82">
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>116</v>
+        <v>81</v>
       </c>
     </row>
     <row r="83">
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>117</v>
+        <v>82</v>
       </c>
     </row>
     <row r="84">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>118</v>
+        <v>83</v>
       </c>
     </row>
     <row r="85">
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>119</v>
+        <v>84</v>
       </c>
     </row>
     <row r="86">
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
     </row>
     <row r="87">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>121</v>
+        <v>86</v>
       </c>
     </row>
     <row r="88">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>122</v>
+        <v>87</v>
       </c>
     </row>
     <row r="89">
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>123</v>
+        <v>88</v>
       </c>
     </row>
     <row r="90">
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>124</v>
+        <v>89</v>
       </c>
     </row>
     <row r="91">
@@ -2235,7 +2235,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
     </row>
     <row r="92">
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>126</v>
+        <v>91</v>
       </c>
     </row>
     <row r="93">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>127</v>
+        <v>92</v>
       </c>
     </row>
     <row r="94">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>128</v>
+        <v>93</v>
       </c>
     </row>
     <row r="95">
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>129</v>
+        <v>94</v>
       </c>
     </row>
     <row r="96">
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
     </row>
     <row r="97">
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>131</v>
+        <v>96</v>
       </c>
     </row>
     <row r="98">
@@ -2375,7 +2375,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>132</v>
+        <v>97</v>
       </c>
     </row>
     <row r="99">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>133</v>
+        <v>98</v>
       </c>
     </row>
     <row r="100">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>134</v>
+        <v>99</v>
       </c>
     </row>
     <row r="101">
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>135</v>
+        <v>100</v>
       </c>
     </row>
     <row r="102">
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>136</v>
+        <v>101</v>
       </c>
     </row>
     <row r="103">
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>137</v>
+        <v>102</v>
       </c>
     </row>
     <row r="104">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>138</v>
+        <v>103</v>
       </c>
     </row>
     <row r="105">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>139</v>
+        <v>104</v>
       </c>
     </row>
     <row r="106">
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>140</v>
+        <v>105</v>
       </c>
     </row>
     <row r="107">
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>141</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/students_data.xlsx
+++ b/students_data.xlsx
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="57">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
     </row>
     <row r="58">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
     </row>
     <row r="60">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="61">
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="62">
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="63">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="64">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="65">
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
     </row>
     <row r="66">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="67">
@@ -1755,7 +1755,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="69">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="70">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="71">
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="72">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="73">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="74">
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
     </row>
     <row r="75">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
     </row>
     <row r="76">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="77">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="78">
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
     </row>
     <row r="79">
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
     </row>
     <row r="80">
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
     </row>
     <row r="81">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
     </row>
     <row r="82">
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>81</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83">
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>82</v>
+        <v>117</v>
       </c>
     </row>
     <row r="84">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>83</v>
+        <v>118</v>
       </c>
     </row>
     <row r="85">
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>84</v>
+        <v>119</v>
       </c>
     </row>
     <row r="86">
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>85</v>
+        <v>120</v>
       </c>
     </row>
     <row r="87">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>86</v>
+        <v>121</v>
       </c>
     </row>
     <row r="88">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>87</v>
+        <v>122</v>
       </c>
     </row>
     <row r="89">
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>88</v>
+        <v>123</v>
       </c>
     </row>
     <row r="90">
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>89</v>
+        <v>124</v>
       </c>
     </row>
     <row r="91">
@@ -2235,7 +2235,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>90</v>
+        <v>125</v>
       </c>
     </row>
     <row r="92">
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>91</v>
+        <v>126</v>
       </c>
     </row>
     <row r="93">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>92</v>
+        <v>127</v>
       </c>
     </row>
     <row r="94">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>93</v>
+        <v>128</v>
       </c>
     </row>
     <row r="95">
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>94</v>
+        <v>129</v>
       </c>
     </row>
     <row r="96">
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>95</v>
+        <v>130</v>
       </c>
     </row>
     <row r="97">
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>96</v>
+        <v>131</v>
       </c>
     </row>
     <row r="98">
@@ -2375,7 +2375,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>97</v>
+        <v>132</v>
       </c>
     </row>
     <row r="99">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>98</v>
+        <v>133</v>
       </c>
     </row>
     <row r="100">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>99</v>
+        <v>134</v>
       </c>
     </row>
     <row r="101">
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>100</v>
+        <v>135</v>
       </c>
     </row>
     <row r="102">
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>101</v>
+        <v>136</v>
       </c>
     </row>
     <row r="103">
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>102</v>
+        <v>137</v>
       </c>
     </row>
     <row r="104">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>103</v>
+        <v>138</v>
       </c>
     </row>
     <row r="105">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>104</v>
+        <v>139</v>
       </c>
     </row>
     <row r="106">
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>105</v>
+        <v>140</v>
       </c>
     </row>
     <row r="107">
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>106</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/students_data.xlsx
+++ b/students_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aburakanalhazmi/Desktop/shawahed_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2A31C51-A95E-0548-9F7C-24DB069BBDD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6AEF1A4-AE18-FC4C-A528-DCD727B502B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="17220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="218">
   <si>
     <t>اسم الطالب</t>
   </si>
@@ -242,9 +242,6 @@
   </si>
   <si>
     <t>خليل بن إبراهيم بن مضوي فقيهي</t>
-  </si>
-  <si>
-    <t>1170643603</t>
   </si>
   <si>
     <t>راكان بن يحي بن حسن معدلي</t>
@@ -1061,7 +1058,7 @@
         <v>6</v>
       </c>
       <c r="D2" s="1">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.15">
@@ -1530,8 +1527,8 @@
       <c r="A36" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>74</v>
+      <c r="B36" s="1">
+        <v>1170643603</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>57</v>
@@ -1542,10 +1539,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>57</v>
@@ -1556,10 +1553,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A38" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>57</v>
@@ -1570,10 +1567,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A39" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>57</v>
@@ -1584,10 +1581,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A40" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>57</v>
@@ -1598,10 +1595,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A41" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>57</v>
@@ -1612,10 +1609,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A42" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>57</v>
@@ -1626,10 +1623,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A43" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>57</v>
@@ -1640,10 +1637,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>57</v>
@@ -1654,10 +1651,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>57</v>
@@ -1668,10 +1665,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>57</v>
@@ -1682,10 +1679,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>57</v>
@@ -1696,10 +1693,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>57</v>
@@ -1710,10 +1707,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>57</v>
@@ -1724,10 +1721,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>57</v>
@@ -1738,10 +1735,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>57</v>
@@ -1752,10 +1749,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>57</v>
@@ -1766,10 +1763,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>57</v>
@@ -1780,10 +1777,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>57</v>
@@ -1794,10 +1791,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>57</v>
@@ -1808,13 +1805,13 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="C56" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="D56" s="1">
         <v>55</v>
@@ -1822,13 +1819,13 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="C57" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D57" s="1">
         <v>56</v>
@@ -1836,13 +1833,13 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="C58" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D58" s="1">
         <v>57</v>
@@ -1850,13 +1847,13 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="C59" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D59" s="1">
         <v>58</v>
@@ -1864,13 +1861,13 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="C60" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D60" s="1">
         <v>59</v>
@@ -1878,13 +1875,13 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="C61" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D61" s="1">
         <v>60</v>
@@ -1892,13 +1889,13 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="C62" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D62" s="1">
         <v>61</v>
@@ -1906,13 +1903,13 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="C63" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D63" s="1">
         <v>62</v>
@@ -1920,13 +1917,13 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="C64" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D64" s="1">
         <v>63</v>
@@ -1934,13 +1931,13 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="C65" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D65" s="1">
         <v>64</v>
@@ -1948,13 +1945,13 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="C66" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D66" s="1">
         <v>65</v>
@@ -1962,13 +1959,13 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="C67" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D67" s="1">
         <v>66</v>
@@ -1976,13 +1973,13 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="C68" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D68" s="1">
         <v>67</v>
@@ -1990,13 +1987,13 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="C69" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D69" s="1">
         <v>68</v>
@@ -2004,13 +2001,13 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>143</v>
-      </c>
       <c r="C70" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D70" s="1">
         <v>69</v>
@@ -2018,13 +2015,13 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A71" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>145</v>
-      </c>
       <c r="C71" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D71" s="1">
         <v>70</v>
@@ -2032,13 +2029,13 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A72" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>147</v>
-      </c>
       <c r="C72" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D72" s="1">
         <v>71</v>
@@ -2046,13 +2043,13 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A73" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="C73" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D73" s="1">
         <v>72</v>
@@ -2060,13 +2057,13 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A74" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="C74" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D74" s="1">
         <v>73</v>
@@ -2074,13 +2071,13 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A75" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="C75" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D75" s="1">
         <v>74</v>
@@ -2088,13 +2085,13 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A76" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="C76" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D76" s="1">
         <v>75</v>
@@ -2102,13 +2099,13 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A77" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="C77" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D77" s="1">
         <v>76</v>
@@ -2116,13 +2113,13 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A78" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="C78" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D78" s="1">
         <v>77</v>
@@ -2130,13 +2127,13 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A79" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="C79" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D79" s="1">
         <v>78</v>
@@ -2144,13 +2141,13 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A80" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="C80" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D80" s="1">
         <v>79</v>
@@ -2158,13 +2155,13 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A81" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="C81" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D81" s="1">
         <v>80</v>
@@ -2172,13 +2169,13 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A82" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="C82" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>168</v>
       </c>
       <c r="D82" s="1">
         <v>81</v>
@@ -2186,13 +2183,13 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A83" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="C83" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D83" s="1">
         <v>82</v>
@@ -2200,13 +2197,13 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A84" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>172</v>
-      </c>
       <c r="C84" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D84" s="1">
         <v>83</v>
@@ -2214,13 +2211,13 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A85" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="C85" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D85" s="1">
         <v>84</v>
@@ -2228,13 +2225,13 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A86" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>176</v>
-      </c>
       <c r="C86" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D86" s="1">
         <v>85</v>
@@ -2242,13 +2239,13 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A87" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>178</v>
-      </c>
       <c r="C87" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D87" s="1">
         <v>86</v>
@@ -2256,13 +2253,13 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A88" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>180</v>
-      </c>
       <c r="C88" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D88" s="1">
         <v>87</v>
@@ -2270,13 +2267,13 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A89" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="C89" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D89" s="1">
         <v>88</v>
@@ -2284,13 +2281,13 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A90" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="C90" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D90" s="1">
         <v>89</v>
@@ -2298,13 +2295,13 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A91" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="C91" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D91" s="1">
         <v>90</v>
@@ -2312,13 +2309,13 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A92" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="C92" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D92" s="1">
         <v>91</v>
@@ -2326,13 +2323,13 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A93" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="C93" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D93" s="1">
         <v>92</v>
@@ -2340,13 +2337,13 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A94" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="C94" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D94" s="1">
         <v>93</v>
@@ -2354,13 +2351,13 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A95" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="C95" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D95" s="1">
         <v>94</v>
@@ -2368,13 +2365,13 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A96" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="C96" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D96" s="1">
         <v>95</v>
@@ -2382,13 +2379,13 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A97" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="C97" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D97" s="1">
         <v>96</v>
@@ -2396,13 +2393,13 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A98" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="C98" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D98" s="1">
         <v>97</v>
@@ -2410,13 +2407,13 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A99" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="C99" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D99" s="1">
         <v>98</v>
@@ -2424,13 +2421,13 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A100" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="C100" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D100" s="1">
         <v>99</v>
@@ -2438,13 +2435,13 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A101" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="C101" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D101" s="1">
         <v>100</v>
@@ -2452,13 +2449,13 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A102" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C102" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D102" s="1">
         <v>101</v>
@@ -2466,13 +2463,13 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A103" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="C103" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D103" s="1">
         <v>102</v>
@@ -2480,13 +2477,13 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A104" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="C104" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D104" s="1">
         <v>103</v>
@@ -2494,13 +2491,13 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A105" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="C105" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D105" s="1">
         <v>104</v>
@@ -2508,13 +2505,13 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A106" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="C106" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D106" s="1">
         <v>105</v>
@@ -2522,13 +2519,13 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A107" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="C107" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D107" s="1">
         <v>106</v>
@@ -2536,5 +2533,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/students_data.xlsx
+++ b/students_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aburakanalhazmi/Desktop/shawahed_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6AEF1A4-AE18-FC4C-A528-DCD727B502B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{808868AD-7B4C-7841-B7DC-008352D01672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="269">
   <si>
     <t>اسم الطالب</t>
   </si>
@@ -674,13 +674,166 @@
   </si>
   <si>
     <t>1159319043</t>
+  </si>
+  <si>
+    <t>محمد بن حسين بن محزوم</t>
+  </si>
+  <si>
+    <t>محمد بن عبدالرحمن الرفاعي</t>
+  </si>
+  <si>
+    <t>محمد بن عبدالكريم بن محمد خواجي</t>
+  </si>
+  <si>
+    <t>محمد بن عبده بن سلطان دغري</t>
+  </si>
+  <si>
+    <t>مهند تركي جابر محمد مجرشي</t>
+  </si>
+  <si>
+    <t>نادر بن يحي بن أحمد خواجي</t>
+  </si>
+  <si>
+    <t>يوسف بن حسين بن موسى محمد</t>
+  </si>
+  <si>
+    <t>قاسم دوران حسين جبالي</t>
+  </si>
+  <si>
+    <t>أحمد حسين علي مشطا</t>
+  </si>
+  <si>
+    <t>AA40652652</t>
+  </si>
+  <si>
+    <t>احمد بن قاسم بن محمد الاعرج</t>
+  </si>
+  <si>
+    <t>عبدالله زيد قطيل ال حسين</t>
+  </si>
+  <si>
+    <t>AA41121</t>
+  </si>
+  <si>
+    <t>عمار عبده قطيل ال حسين</t>
+  </si>
+  <si>
+    <t>40702aa</t>
+  </si>
+  <si>
+    <t>مؤيد بن مفرح بن محمد مرزوق</t>
+  </si>
+  <si>
+    <t>ماجد صالح سعيد عبده</t>
+  </si>
+  <si>
+    <t>ماهر بن يحيى بن احمد بن حسين خواجي</t>
+  </si>
+  <si>
+    <t>محمد ابراهيم محمد جعيدي</t>
+  </si>
+  <si>
+    <t>محمد بن احمد بن محمد شبيلي</t>
+  </si>
+  <si>
+    <t>محمد بن هاشم بن حسين خواجي</t>
+  </si>
+  <si>
+    <t>مراد محمد محمد دهل</t>
+  </si>
+  <si>
+    <t>مشعل عبدالعزيز عباس عريشي</t>
+  </si>
+  <si>
+    <t>معاذ بن محمد بن احمد بن يحي شويعي</t>
+  </si>
+  <si>
+    <t>مهند عبدالله ابراهيم القيسي</t>
+  </si>
+  <si>
+    <t>موسى قربع يحي الريثي</t>
+  </si>
+  <si>
+    <t>ناصر ابراهيم احمد ضيف الله</t>
+  </si>
+  <si>
+    <t>هادي محمد هادي هادي</t>
+  </si>
+  <si>
+    <t>هادي منصور هباش هادي</t>
+  </si>
+  <si>
+    <t>وسام احمد محمد جلال</t>
+  </si>
+  <si>
+    <t>وسام بن فواز بن حسين بن حسن شولان</t>
+  </si>
+  <si>
+    <t>وليد محمد صلاح حكمي</t>
+  </si>
+  <si>
+    <t>يحيى بن محمد بن علي العبسي</t>
+  </si>
+  <si>
+    <t>يحيى هادي يحي علي</t>
+  </si>
+  <si>
+    <t>يزن ثابت احمد عاتي</t>
+  </si>
+  <si>
+    <t>يوسف عبدالله احمد القيسي</t>
+  </si>
+  <si>
+    <t>يوسف محمد احمد صالح</t>
+  </si>
+  <si>
+    <t>a401261</t>
+  </si>
+  <si>
+    <t>A2937</t>
+  </si>
+  <si>
+    <t>B2937</t>
+  </si>
+  <si>
+    <t>احمد ماجد علي ال حسين</t>
+  </si>
+  <si>
+    <t>3912686530a</t>
+  </si>
+  <si>
+    <t>حسن حسين علي مشطا</t>
+  </si>
+  <si>
+    <t>39372060a</t>
+  </si>
+  <si>
+    <t>خالد زيد قطيل ال حسين</t>
+  </si>
+  <si>
+    <t>خليل احمد احمد اسماعيل كناني</t>
+  </si>
+  <si>
+    <t>40432505aa</t>
+  </si>
+  <si>
+    <t>معاذ عبدالله حسين ابوعبسي</t>
+  </si>
+  <si>
+    <t>نايف حسن محمد هزازي</t>
+  </si>
+  <si>
+    <t>نايف علي باري غروي</t>
+  </si>
+  <si>
+    <t>نايف محمد أحمد هندوان</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -691,6 +844,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -717,9 +878,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1024,7 +1188,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D107"/>
+  <dimension ref="A1:D149"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="45" style="1" customWidth="1"/>
@@ -1408,7 +1572,7 @@
         <v>57</v>
       </c>
       <c r="D27" s="1">
-        <v>26</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.15">
@@ -1422,7 +1586,7 @@
         <v>57</v>
       </c>
       <c r="D28" s="1">
-        <v>27</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.15">
@@ -1436,7 +1600,7 @@
         <v>57</v>
       </c>
       <c r="D29" s="1">
-        <v>28</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.15">
@@ -1450,7 +1614,7 @@
         <v>57</v>
       </c>
       <c r="D30" s="1">
-        <v>29</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.15">
@@ -1464,7 +1628,7 @@
         <v>57</v>
       </c>
       <c r="D31" s="1">
-        <v>30</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.15">
@@ -1478,7 +1642,7 @@
         <v>57</v>
       </c>
       <c r="D32" s="1">
-        <v>31</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.15">
@@ -1492,7 +1656,7 @@
         <v>57</v>
       </c>
       <c r="D33" s="1">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.15">
@@ -1506,7 +1670,7 @@
         <v>57</v>
       </c>
       <c r="D34" s="1">
-        <v>33</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.15">
@@ -1520,7 +1684,7 @@
         <v>57</v>
       </c>
       <c r="D35" s="1">
-        <v>34</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.15">
@@ -1534,7 +1698,7 @@
         <v>57</v>
       </c>
       <c r="D36" s="1">
-        <v>35</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.15">
@@ -1548,7 +1712,7 @@
         <v>57</v>
       </c>
       <c r="D37" s="1">
-        <v>36</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.15">
@@ -1562,7 +1726,7 @@
         <v>57</v>
       </c>
       <c r="D38" s="1">
-        <v>37</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.15">
@@ -1576,7 +1740,7 @@
         <v>57</v>
       </c>
       <c r="D39" s="1">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.15">
@@ -1590,7 +1754,7 @@
         <v>57</v>
       </c>
       <c r="D40" s="1">
-        <v>39</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.15">
@@ -1604,7 +1768,7 @@
         <v>57</v>
       </c>
       <c r="D41" s="1">
-        <v>40</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.15">
@@ -1618,7 +1782,7 @@
         <v>57</v>
       </c>
       <c r="D42" s="1">
-        <v>41</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.15">
@@ -1632,7 +1796,7 @@
         <v>57</v>
       </c>
       <c r="D43" s="1">
-        <v>42</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.15">
@@ -1646,7 +1810,7 @@
         <v>57</v>
       </c>
       <c r="D44" s="1">
-        <v>43</v>
+        <v>80</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.15">
@@ -1660,7 +1824,7 @@
         <v>57</v>
       </c>
       <c r="D45" s="1">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.15">
@@ -1674,7 +1838,7 @@
         <v>57</v>
       </c>
       <c r="D46" s="1">
-        <v>45</v>
+        <v>81</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.15">
@@ -1688,7 +1852,7 @@
         <v>57</v>
       </c>
       <c r="D47" s="1">
-        <v>46</v>
+        <v>61</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.15">
@@ -1702,7 +1866,7 @@
         <v>57</v>
       </c>
       <c r="D48" s="1">
-        <v>47</v>
+        <v>62</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.15">
@@ -1716,7 +1880,7 @@
         <v>57</v>
       </c>
       <c r="D49" s="1">
-        <v>48</v>
+        <v>82</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.15">
@@ -1730,7 +1894,7 @@
         <v>57</v>
       </c>
       <c r="D50" s="1">
-        <v>49</v>
+        <v>83</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.15">
@@ -1744,7 +1908,7 @@
         <v>57</v>
       </c>
       <c r="D51" s="1">
-        <v>50</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.15">
@@ -1758,7 +1922,7 @@
         <v>57</v>
       </c>
       <c r="D52" s="1">
-        <v>51</v>
+        <v>63</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.15">
@@ -1772,7 +1936,7 @@
         <v>57</v>
       </c>
       <c r="D53" s="1">
-        <v>52</v>
+        <v>65</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.15">
@@ -1786,7 +1950,7 @@
         <v>57</v>
       </c>
       <c r="D54" s="1">
-        <v>53</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.15">
@@ -1800,7 +1964,7 @@
         <v>57</v>
       </c>
       <c r="D55" s="1">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.15">
@@ -1828,7 +1992,7 @@
         <v>114</v>
       </c>
       <c r="D57" s="1">
-        <v>56</v>
+        <v>90</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.15">
@@ -1842,7 +2006,7 @@
         <v>114</v>
       </c>
       <c r="D58" s="1">
-        <v>57</v>
+        <v>91</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.15">
@@ -1870,7 +2034,7 @@
         <v>114</v>
       </c>
       <c r="D60" s="1">
-        <v>59</v>
+        <v>92</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.15">
@@ -1968,7 +2132,7 @@
         <v>114</v>
       </c>
       <c r="D67" s="1">
-        <v>66</v>
+        <v>94</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.15">
@@ -1982,7 +2146,7 @@
         <v>114</v>
       </c>
       <c r="D68" s="1">
-        <v>67</v>
+        <v>95</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.15">
@@ -2010,7 +2174,7 @@
         <v>114</v>
       </c>
       <c r="D70" s="1">
-        <v>69</v>
+        <v>96</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.15">
@@ -2066,7 +2230,7 @@
         <v>114</v>
       </c>
       <c r="D74" s="1">
-        <v>73</v>
+        <v>97</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.15">
@@ -2122,7 +2286,7 @@
         <v>114</v>
       </c>
       <c r="D78" s="1">
-        <v>77</v>
+        <v>98</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.15">
@@ -2164,7 +2328,7 @@
         <v>114</v>
       </c>
       <c r="D81" s="1">
-        <v>80</v>
+        <v>107</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.15">
@@ -2178,7 +2342,7 @@
         <v>167</v>
       </c>
       <c r="D82" s="1">
-        <v>81</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.15">
@@ -2192,7 +2356,7 @@
         <v>167</v>
       </c>
       <c r="D83" s="1">
-        <v>82</v>
+        <v>117</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.15">
@@ -2206,7 +2370,7 @@
         <v>167</v>
       </c>
       <c r="D84" s="1">
-        <v>83</v>
+        <v>118</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.15">
@@ -2220,7 +2384,7 @@
         <v>167</v>
       </c>
       <c r="D85" s="1">
-        <v>84</v>
+        <v>120</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.15">
@@ -2234,7 +2398,7 @@
         <v>167</v>
       </c>
       <c r="D86" s="1">
-        <v>85</v>
+        <v>121</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.15">
@@ -2248,7 +2412,7 @@
         <v>167</v>
       </c>
       <c r="D87" s="1">
-        <v>86</v>
+        <v>122</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.15">
@@ -2262,7 +2426,7 @@
         <v>167</v>
       </c>
       <c r="D88" s="1">
-        <v>87</v>
+        <v>123</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.15">
@@ -2276,7 +2440,7 @@
         <v>167</v>
       </c>
       <c r="D89" s="1">
-        <v>88</v>
+        <v>126</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.15">
@@ -2290,7 +2454,7 @@
         <v>167</v>
       </c>
       <c r="D90" s="1">
-        <v>89</v>
+        <v>128</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.15">
@@ -2304,7 +2468,7 @@
         <v>167</v>
       </c>
       <c r="D91" s="1">
-        <v>90</v>
+        <v>129</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.15">
@@ -2318,7 +2482,7 @@
         <v>167</v>
       </c>
       <c r="D92" s="1">
-        <v>91</v>
+        <v>131</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.15">
@@ -2332,7 +2496,7 @@
         <v>167</v>
       </c>
       <c r="D93" s="1">
-        <v>92</v>
+        <v>130</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.15">
@@ -2346,7 +2510,7 @@
         <v>167</v>
       </c>
       <c r="D94" s="1">
-        <v>93</v>
+        <v>132</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.15">
@@ -2360,7 +2524,7 @@
         <v>167</v>
       </c>
       <c r="D95" s="1">
-        <v>94</v>
+        <v>133</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.15">
@@ -2374,7 +2538,7 @@
         <v>167</v>
       </c>
       <c r="D96" s="1">
-        <v>95</v>
+        <v>134</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.15">
@@ -2388,7 +2552,7 @@
         <v>167</v>
       </c>
       <c r="D97" s="1">
-        <v>96</v>
+        <v>135</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.15">
@@ -2402,7 +2566,7 @@
         <v>167</v>
       </c>
       <c r="D98" s="1">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.15">
@@ -2416,7 +2580,7 @@
         <v>167</v>
       </c>
       <c r="D99" s="1">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.15">
@@ -2430,7 +2594,7 @@
         <v>167</v>
       </c>
       <c r="D100" s="1">
-        <v>99</v>
+        <v>138</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.15">
@@ -2444,7 +2608,7 @@
         <v>167</v>
       </c>
       <c r="D101" s="1">
-        <v>100</v>
+        <v>139</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.15">
@@ -2458,7 +2622,7 @@
         <v>167</v>
       </c>
       <c r="D102" s="1">
-        <v>101</v>
+        <v>140</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.15">
@@ -2472,7 +2636,7 @@
         <v>167</v>
       </c>
       <c r="D103" s="1">
-        <v>102</v>
+        <v>141</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.15">
@@ -2486,7 +2650,7 @@
         <v>167</v>
       </c>
       <c r="D104" s="1">
-        <v>103</v>
+        <v>142</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.15">
@@ -2500,7 +2664,7 @@
         <v>167</v>
       </c>
       <c r="D105" s="1">
-        <v>104</v>
+        <v>144</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.15">
@@ -2514,7 +2678,7 @@
         <v>167</v>
       </c>
       <c r="D106" s="1">
-        <v>105</v>
+        <v>145</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.15">
@@ -2528,7 +2692,592 @@
         <v>167</v>
       </c>
       <c r="D107" s="1">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A108" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B108" s="1">
+        <v>1171904780</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D108" s="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A109" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B109" s="1">
+        <v>1170366247</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D109" s="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A110" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B110" s="1">
+        <v>1167502283</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D110" s="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A111" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B111" s="1">
+        <v>1172242503</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D111" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A112" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B112" s="1">
+        <v>1173217702</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D112" s="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A113" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B113" s="1">
+        <v>1168684411</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D113" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A114" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B114" s="1">
+        <v>1172306696</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D114" s="1">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A115" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B115" s="1">
+        <v>8885500012</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D115" s="1">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A116" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D116" s="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A117" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B117" s="1">
+        <v>1163250507</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D117" s="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A118" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D118" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A119" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D119" s="1">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A120" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B120" s="1">
+        <v>1165324110</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D120" s="1">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A121" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B121" s="1">
+        <v>4148138052</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D121" s="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A122" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B122" s="1">
+        <v>1164420844</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D122" s="1">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A123" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B123" s="1">
+        <v>4615745579</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D123" s="1">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A124" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B124" s="1">
+        <v>1181813641</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D124" s="1">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A125" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B125" s="1">
+        <v>1163831744</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D125" s="1">
         <v>106</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A126" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B126" s="1">
+        <v>4147413001</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D126" s="1">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A127" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B127" s="1">
+        <v>1163490434</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D127" s="1">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A128" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D128" s="1">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A129" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D129" s="1">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A130" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B130" s="1">
+        <v>1157574326</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D130" s="1">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A131" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B131" s="1">
+        <v>4158162166</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D131" s="1">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A132" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B132" s="1">
+        <v>2423235403</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D132" s="1">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A133" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B133" s="1">
+        <v>4161468287</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D133" s="1">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A134" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B134" s="1">
+        <v>1164394189</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D134" s="1">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A135" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B135" s="1">
+        <v>1164072280</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D135" s="1">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A136" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B136" s="1">
+        <v>4146865078</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D136" s="1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A137" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B137" s="1">
+        <v>1167047925</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D137" s="1">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A138" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B138" s="1">
+        <v>2358054076</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D138" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A139" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B139" s="1">
+        <v>1167005832</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D139" s="1">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A140" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D140" s="1">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A141" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B141" s="1">
+        <v>4148138326</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D141" s="1">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A142" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D142" s="1">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A143" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D143" s="1">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A144" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B144" s="1">
+        <v>39357241</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D144" s="1">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A145" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D145" s="1">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A146" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B146" s="1">
+        <v>1164514281</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D146" s="1">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A147" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B147" s="1">
+        <v>1161684004</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D147" s="1">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A148" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B148" s="1">
+        <v>1161411887</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D148" s="1">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A149" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B149" s="1">
+        <v>170498263</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/students_data.xlsx
+++ b/students_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aburakanalhazmi/Desktop/shawahed_project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aburakanalhazmi/shawahed_local/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{808868AD-7B4C-7841-B7DC-008352D01672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDF452BC-6D09-DA45-91A0-ADFDF7CE19C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="17220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -833,7 +833,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -857,6 +857,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -875,8 +882,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -887,8 +895,9 @@
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="1" xr:uid="{547660EB-2ECC-7847-AA09-94C772084EC8}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1978,7 +1987,7 @@
         <v>114</v>
       </c>
       <c r="D56" s="1">
-        <v>55</v>
+        <v>155</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.15">
@@ -2020,7 +2029,7 @@
         <v>114</v>
       </c>
       <c r="D59" s="1">
-        <v>58</v>
+        <v>156</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.15">
@@ -2048,7 +2057,7 @@
         <v>114</v>
       </c>
       <c r="D61" s="1">
-        <v>60</v>
+        <v>157</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.15">
@@ -2062,7 +2071,7 @@
         <v>114</v>
       </c>
       <c r="D62" s="1">
-        <v>61</v>
+        <v>158</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.15">
@@ -2076,7 +2085,7 @@
         <v>114</v>
       </c>
       <c r="D63" s="1">
-        <v>62</v>
+        <v>159</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.15">
@@ -2104,7 +2113,7 @@
         <v>114</v>
       </c>
       <c r="D65" s="1">
-        <v>64</v>
+        <v>160</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.15">
@@ -2118,7 +2127,7 @@
         <v>114</v>
       </c>
       <c r="D66" s="1">
-        <v>65</v>
+        <v>161</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.15">
@@ -2160,7 +2169,7 @@
         <v>114</v>
       </c>
       <c r="D69" s="1">
-        <v>68</v>
+        <v>162</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.15">
@@ -2188,7 +2197,7 @@
         <v>114</v>
       </c>
       <c r="D71" s="1">
-        <v>70</v>
+        <v>163</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.15">
@@ -2202,7 +2211,7 @@
         <v>114</v>
       </c>
       <c r="D72" s="1">
-        <v>71</v>
+        <v>164</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.15">
@@ -2216,7 +2225,7 @@
         <v>114</v>
       </c>
       <c r="D73" s="1">
-        <v>72</v>
+        <v>165</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.15">
@@ -2244,7 +2253,7 @@
         <v>114</v>
       </c>
       <c r="D75" s="1">
-        <v>74</v>
+        <v>166</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.15">
@@ -2258,7 +2267,7 @@
         <v>114</v>
       </c>
       <c r="D76" s="1">
-        <v>75</v>
+        <v>167</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.15">
@@ -2272,7 +2281,7 @@
         <v>114</v>
       </c>
       <c r="D77" s="1">
-        <v>76</v>
+        <v>168</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.15">
@@ -2300,7 +2309,7 @@
         <v>114</v>
       </c>
       <c r="D79" s="1">
-        <v>78</v>
+        <v>169</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.15">
@@ -2314,7 +2323,7 @@
         <v>114</v>
       </c>
       <c r="D80" s="1">
-        <v>79</v>
+        <v>170</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.15">
@@ -2958,7 +2967,7 @@
         <v>114</v>
       </c>
       <c r="D126" s="1">
-        <v>108</v>
+        <v>171</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.15">
@@ -2986,7 +2995,7 @@
         <v>114</v>
       </c>
       <c r="D128" s="1">
-        <v>110</v>
+        <v>172</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.15">
@@ -3014,7 +3023,7 @@
         <v>114</v>
       </c>
       <c r="D130" s="1">
-        <v>112</v>
+        <v>150</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.15">
@@ -3084,7 +3093,7 @@
         <v>114</v>
       </c>
       <c r="D135" s="1">
-        <v>117</v>
+        <v>151</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.15">
@@ -3098,7 +3107,7 @@
         <v>114</v>
       </c>
       <c r="D136" s="1">
-        <v>118</v>
+        <v>152</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.15">
@@ -3126,7 +3135,7 @@
         <v>114</v>
       </c>
       <c r="D138" s="1">
-        <v>120</v>
+        <v>153</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.15">
@@ -3168,7 +3177,7 @@
         <v>114</v>
       </c>
       <c r="D141" s="1">
-        <v>123</v>
+        <v>154</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.15">

--- a/students_data.xlsx
+++ b/students_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aburakanalhazmi/shawahed_local/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDF452BC-6D09-DA45-91A0-ADFDF7CE19C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73893BBA-3515-F948-AF52-9CA600E314CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="17220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3288,6 +3288,9 @@
       <c r="C149" s="1" t="s">
         <v>167</v>
       </c>
+      <c r="D149" s="1">
+        <v>173</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
